--- a/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/persona/primary_persona_vs_mobile_navigation.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/persona/primary_persona_vs_mobile_navigation.xlsx
@@ -462,10 +462,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
         <v>6</v>
@@ -481,10 +481,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
         <v>5</v>
@@ -503,7 +503,7 @@
         <v>11</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
         <v>4</v>
@@ -525,7 +525,7 @@
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -538,13 +538,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
         <v>3</v>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C7" t="n">
         <v>10</v>
